--- a/etf_holdings/2026-08-24_daily_changes_changed_only.xlsx
+++ b/etf_holdings/2026-08-24_daily_changes_changed_only.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M8"/>
+  <dimension ref="A1:M12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -864,61 +864,313 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>00982A</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2345</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>智邦</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>智邦</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>3.41%</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>3.09%</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>-0.32%</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>817000</v>
+      </c>
+      <c r="K8" t="n">
+        <v>727000</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>-90,000</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>2026-08-22_00982A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>00982A</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>3264</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>欣銓</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>欣銓</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>1.66%</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>1.37%</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>-0.29%</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>3985000</v>
+      </c>
+      <c r="K9" t="n">
+        <v>3242000</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>-743,000</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>2026-08-22_00982A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>00982A</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>6239</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>力成</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>力成</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0.39%</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>1.06%</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>+0.67%</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>710000</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1910000</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>1,200,000</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>2026-08-22_00982A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>00982A</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>6472</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>保瑞</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>保瑞</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>0.48%</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>0.72%</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>+0.24%</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>516000</v>
+      </c>
+      <c r="K11" t="n">
+        <v>774000</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>258,000</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>2026-08-22_00982A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>00403A</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>持續持有</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>加碼</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>2059</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>川湖</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>川湖</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>0.16%</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>0.30%</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>+0.14%</t>
         </is>
       </c>
-      <c r="J8" t="n">
+      <c r="J12" t="n">
         <v>20000</v>
       </c>
-      <c r="K8" t="n">
+      <c r="K12" t="n">
         <v>35000</v>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>15,000</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>2026-08-22_00403A_full_holdings.xlsx</t>
         </is>

--- a/etf_holdings/2026-08-24_daily_changes_changed_only.xlsx
+++ b/etf_holdings/2026-08-24_daily_changes_changed_only.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M12"/>
+  <dimension ref="A1:M8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -864,7 +864,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>00982A</t>
+          <t>00403A</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -874,303 +874,51 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>2059</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>智邦</t>
+          <t>川湖</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>智邦</t>
+          <t>川湖</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>3.41%</t>
+          <t>0.16%</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>3.09%</t>
+          <t>0.30%</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-0.32%</t>
+          <t>+0.14%</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>817000</v>
+        <v>20000</v>
       </c>
       <c r="K8" t="n">
-        <v>727000</v>
+        <v>35000</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-90,000</t>
+          <t>15,000</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
-        <is>
-          <t>2026-08-22_00982A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>00982A</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>減碼</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>3264</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>欣銓</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>欣銓</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>1.66%</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>1.37%</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>-0.29%</t>
-        </is>
-      </c>
-      <c r="J9" t="n">
-        <v>3985000</v>
-      </c>
-      <c r="K9" t="n">
-        <v>3242000</v>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>-743,000</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>2026-08-22_00982A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>00982A</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>加碼</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>6239</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>力成</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>力成</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>0.39%</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>1.06%</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>+0.67%</t>
-        </is>
-      </c>
-      <c r="J10" t="n">
-        <v>710000</v>
-      </c>
-      <c r="K10" t="n">
-        <v>1910000</v>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>1,200,000</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>2026-08-22_00982A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>00982A</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>加碼</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>6472</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>保瑞</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>保瑞</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>0.48%</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>0.72%</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>+0.24%</t>
-        </is>
-      </c>
-      <c r="J11" t="n">
-        <v>516000</v>
-      </c>
-      <c r="K11" t="n">
-        <v>774000</v>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>258,000</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>2026-08-22_00982A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>00403A</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>加碼</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>2059</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>川湖</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>川湖</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>0.16%</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>0.30%</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>+0.14%</t>
-        </is>
-      </c>
-      <c r="J12" t="n">
-        <v>20000</v>
-      </c>
-      <c r="K12" t="n">
-        <v>35000</v>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>15,000</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
         <is>
           <t>2026-08-22_00403A_full_holdings.xlsx</t>
         </is>
